--- a/resultados/adrianopolis/inventario_links.xlsx
+++ b/resultados/adrianopolis/inventario_links.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I154"/>
+  <dimension ref="A1:J294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,11 @@
           <t>data_varredura</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>status_download</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -505,6 +510,11 @@
           <t>2026-07-29 10:37:19</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -548,6 +558,11 @@
           <t>2026-07-29 10:37:20</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -591,6 +606,11 @@
           <t>2026-07-29 10:37:21</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -634,6 +654,11 @@
           <t>2026-07-29 10:37:22</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -677,6 +702,11 @@
           <t>2026-07-29 10:37:24</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -720,6 +750,11 @@
           <t>2026-07-29 10:37:25</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -763,6 +798,11 @@
           <t>2026-07-29 10:37:25</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -806,6 +846,11 @@
           <t>2026-07-29 10:37:26</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -849,6 +894,11 @@
           <t>2026-07-29 10:37:27</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -892,6 +942,11 @@
           <t>2026-07-29 10:37:28</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -935,6 +990,11 @@
           <t>2026-07-29 10:37:29</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -978,6 +1038,11 @@
           <t>2026-07-29 10:37:30</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1021,6 +1086,11 @@
           <t>2026-07-29 10:37:30</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1064,6 +1134,11 @@
           <t>2026-07-29 10:37:31</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1107,6 +1182,11 @@
           <t>2026-07-29 10:37:32</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1150,6 +1230,11 @@
           <t>2026-07-29 10:37:33</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1193,6 +1278,11 @@
           <t>2026-07-29 10:37:34</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1236,6 +1326,11 @@
           <t>2026-07-29 10:37:34</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1279,6 +1374,11 @@
           <t>2026-07-29 10:37:35</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1322,6 +1422,11 @@
           <t>2026-07-29 10:37:36</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1365,6 +1470,11 @@
           <t>2026-07-29 10:37:37</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1408,6 +1518,11 @@
           <t>2026-07-29 10:37:38</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1451,6 +1566,11 @@
           <t>2026-07-29 10:37:38</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1494,6 +1614,11 @@
           <t>2026-07-29 10:37:39</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1537,6 +1662,11 @@
           <t>2026-07-29 10:37:40</t>
         </is>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1580,6 +1710,11 @@
           <t>2026-07-29 10:37:41</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1623,6 +1758,11 @@
           <t>2026-07-29 10:37:42</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1666,6 +1806,11 @@
           <t>2026-07-29 10:37:43</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1709,6 +1854,11 @@
           <t>2026-07-29 10:37:43</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1752,6 +1902,11 @@
           <t>2026-07-29 10:37:44</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1795,6 +1950,11 @@
           <t>2026-07-29 10:37:45</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1838,6 +1998,11 @@
           <t>2026-07-29 10:37:46</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1881,6 +2046,11 @@
           <t>2026-07-29 10:37:47</t>
         </is>
       </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1924,6 +2094,11 @@
           <t>2026-07-29 10:37:47</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1967,6 +2142,11 @@
           <t>2026-07-29 10:37:48</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2010,6 +2190,11 @@
           <t>2026-07-29 10:37:49</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2053,6 +2238,11 @@
           <t>2026-07-29 10:37:50</t>
         </is>
       </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2096,6 +2286,11 @@
           <t>2026-07-29 10:37:51</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2139,6 +2334,11 @@
           <t>2026-07-29 10:37:51</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2182,6 +2382,11 @@
           <t>2026-07-29 10:37:52</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2225,6 +2430,11 @@
           <t>2026-07-29 10:37:53</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2268,6 +2478,11 @@
           <t>2026-07-29 10:37:54</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2311,6 +2526,11 @@
           <t>2026-07-29 10:37:55</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2354,6 +2574,11 @@
           <t>2026-07-29 10:37:55</t>
         </is>
       </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2397,6 +2622,11 @@
           <t>2026-07-29 10:37:56</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2440,6 +2670,11 @@
           <t>2026-07-29 10:37:57</t>
         </is>
       </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2483,6 +2718,11 @@
           <t>2026-07-29 10:37:58</t>
         </is>
       </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2526,6 +2766,11 @@
           <t>2026-07-29 10:37:59</t>
         </is>
       </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2569,6 +2814,11 @@
           <t>2026-07-29 10:38:00</t>
         </is>
       </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2612,6 +2862,11 @@
           <t>2026-07-29 10:38:00</t>
         </is>
       </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2655,6 +2910,11 @@
           <t>2026-07-29 10:38:01</t>
         </is>
       </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2698,6 +2958,11 @@
           <t>2026-07-29 10:38:02</t>
         </is>
       </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2741,6 +3006,11 @@
           <t>2026-07-29 10:38:04</t>
         </is>
       </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2784,6 +3054,11 @@
           <t>2026-07-29 10:38:05</t>
         </is>
       </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2827,6 +3102,11 @@
           <t>2026-07-29 10:38:05</t>
         </is>
       </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2870,6 +3150,11 @@
           <t>2026-07-29 10:38:08</t>
         </is>
       </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2913,6 +3198,11 @@
           <t>2026-07-29 10:38:08</t>
         </is>
       </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2956,6 +3246,11 @@
           <t>2026-07-29 10:38:09</t>
         </is>
       </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2999,6 +3294,11 @@
           <t>2026-07-29 10:38:10</t>
         </is>
       </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3042,6 +3342,11 @@
           <t>2026-07-29 10:38:11</t>
         </is>
       </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3085,6 +3390,11 @@
           <t>2026-07-29 10:38:12</t>
         </is>
       </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3128,6 +3438,11 @@
           <t>2026-07-29 10:38:13</t>
         </is>
       </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3171,6 +3486,11 @@
           <t>2026-07-29 10:38:13</t>
         </is>
       </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3214,6 +3534,11 @@
           <t>2026-07-29 10:38:14</t>
         </is>
       </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3257,6 +3582,11 @@
           <t>2026-07-29 10:38:15</t>
         </is>
       </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3300,6 +3630,11 @@
           <t>2026-07-29 10:38:16</t>
         </is>
       </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3343,6 +3678,11 @@
           <t>2026-07-29 10:38:17</t>
         </is>
       </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3386,6 +3726,11 @@
           <t>2026-07-29 10:38:17</t>
         </is>
       </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3429,6 +3774,11 @@
           <t>2026-07-29 10:38:18</t>
         </is>
       </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3472,6 +3822,11 @@
           <t>2026-07-29 10:38:19</t>
         </is>
       </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3515,6 +3870,11 @@
           <t>2026-07-29 10:38:20</t>
         </is>
       </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3558,6 +3918,11 @@
           <t>2026-07-29 10:38:21</t>
         </is>
       </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3601,6 +3966,11 @@
           <t>2026-07-29 10:38:21</t>
         </is>
       </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3644,6 +4014,11 @@
           <t>2026-07-29 10:38:22</t>
         </is>
       </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3687,6 +4062,11 @@
           <t>2026-07-29 10:38:23</t>
         </is>
       </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3730,6 +4110,11 @@
           <t>2026-07-29 10:38:24</t>
         </is>
       </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3773,6 +4158,11 @@
           <t>2026-07-29 10:38:25</t>
         </is>
       </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3816,6 +4206,11 @@
           <t>2026-07-29 10:38:26</t>
         </is>
       </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3859,6 +4254,11 @@
           <t>2026-07-29 10:38:26</t>
         </is>
       </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3902,6 +4302,11 @@
           <t>2026-07-29 10:38:27</t>
         </is>
       </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3945,6 +4350,11 @@
           <t>2026-07-29 10:38:28</t>
         </is>
       </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3988,6 +4398,11 @@
           <t>2026-07-29 10:38:29</t>
         </is>
       </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4031,6 +4446,11 @@
           <t>2026-07-29 10:38:30</t>
         </is>
       </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4074,6 +4494,11 @@
           <t>2026-07-29 10:38:30</t>
         </is>
       </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4117,6 +4542,11 @@
           <t>2026-07-29 10:38:31</t>
         </is>
       </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4160,6 +4590,11 @@
           <t>2026-07-29 10:38:32</t>
         </is>
       </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4203,6 +4638,11 @@
           <t>2026-07-29 10:38:33</t>
         </is>
       </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4246,6 +4686,11 @@
           <t>2026-07-29 10:38:34</t>
         </is>
       </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4289,6 +4734,11 @@
           <t>2026-07-29 10:38:34</t>
         </is>
       </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4332,6 +4782,11 @@
           <t>2026-07-29 10:38:35</t>
         </is>
       </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4375,6 +4830,11 @@
           <t>2026-07-29 10:38:36</t>
         </is>
       </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4418,6 +4878,11 @@
           <t>2026-07-29 10:38:37</t>
         </is>
       </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4461,6 +4926,11 @@
           <t>2026-07-29 10:38:38</t>
         </is>
       </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4504,6 +4974,11 @@
           <t>2026-07-29 10:38:38</t>
         </is>
       </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4547,6 +5022,11 @@
           <t>2026-07-29 10:38:39</t>
         </is>
       </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4590,6 +5070,11 @@
           <t>2026-07-29 10:38:40</t>
         </is>
       </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4633,6 +5118,11 @@
           <t>2026-07-29 10:38:41</t>
         </is>
       </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4676,6 +5166,11 @@
           <t>2026-07-29 10:38:42</t>
         </is>
       </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4719,6 +5214,11 @@
           <t>2026-07-29 10:38:43</t>
         </is>
       </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4762,6 +5262,11 @@
           <t>2026-07-29 10:38:43</t>
         </is>
       </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4805,6 +5310,11 @@
           <t>2026-07-29 10:38:44</t>
         </is>
       </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4848,6 +5358,11 @@
           <t>2026-07-29 10:38:45</t>
         </is>
       </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4891,6 +5406,11 @@
           <t>2026-07-29 10:38:46</t>
         </is>
       </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4934,6 +5454,11 @@
           <t>2026-07-29 10:38:47</t>
         </is>
       </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4977,6 +5502,11 @@
           <t>2026-07-29 10:38:47</t>
         </is>
       </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5020,6 +5550,11 @@
           <t>2026-07-29 10:38:48</t>
         </is>
       </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5063,6 +5598,11 @@
           <t>2026-07-29 10:38:49</t>
         </is>
       </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5106,6 +5646,11 @@
           <t>2026-07-29 10:38:51</t>
         </is>
       </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5149,6 +5694,11 @@
           <t>2026-07-29 10:38:52</t>
         </is>
       </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5192,6 +5742,11 @@
           <t>2026-07-29 10:38:52</t>
         </is>
       </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5235,6 +5790,11 @@
           <t>2026-07-29 10:38:54</t>
         </is>
       </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5278,6 +5838,11 @@
           <t>2026-07-29 10:38:58</t>
         </is>
       </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5321,6 +5886,11 @@
           <t>2026-07-29 10:39:00</t>
         </is>
       </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5364,6 +5934,11 @@
           <t>2026-07-29 10:39:02</t>
         </is>
       </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5407,6 +5982,11 @@
           <t>2026-07-29 10:39:19</t>
         </is>
       </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5450,6 +6030,11 @@
           <t>2026-07-29 10:39:20</t>
         </is>
       </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5493,6 +6078,11 @@
           <t>2026-07-29 10:39:20</t>
         </is>
       </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5536,6 +6126,11 @@
           <t>2026-07-29 10:39:21</t>
         </is>
       </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5579,6 +6174,11 @@
           <t>2026-07-29 10:39:22</t>
         </is>
       </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5622,6 +6222,11 @@
           <t>2026-07-29 10:39:23</t>
         </is>
       </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5665,6 +6270,11 @@
           <t>2026-07-29 10:39:25</t>
         </is>
       </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5708,6 +6318,11 @@
           <t>2026-07-29 10:39:30</t>
         </is>
       </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5751,6 +6366,11 @@
           <t>2026-07-29 10:39:32</t>
         </is>
       </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5794,6 +6414,11 @@
           <t>2026-07-29 10:39:34</t>
         </is>
       </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5837,6 +6462,11 @@
           <t>2026-07-29 10:41:55</t>
         </is>
       </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5880,6 +6510,11 @@
           <t>2026-07-29 10:43:52</t>
         </is>
       </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5923,6 +6558,11 @@
           <t>2026-07-29 10:44:04</t>
         </is>
       </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5966,6 +6606,11 @@
           <t>2026-07-29 10:44:05</t>
         </is>
       </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6009,6 +6654,11 @@
           <t>2026-07-29 10:44:07</t>
         </is>
       </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6052,6 +6702,11 @@
           <t>2026-07-29 11:06:01</t>
         </is>
       </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6095,6 +6750,11 @@
           <t>2026-07-29 11:06:02</t>
         </is>
       </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6138,6 +6798,11 @@
           <t>2026-07-29 11:06:02</t>
         </is>
       </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6181,6 +6846,11 @@
           <t>2026-07-29 11:06:02</t>
         </is>
       </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6224,6 +6894,11 @@
           <t>2026-07-29 11:06:03</t>
         </is>
       </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6267,6 +6942,11 @@
           <t>2026-07-29 11:06:04</t>
         </is>
       </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6310,6 +6990,11 @@
           <t>2026-07-29 11:06:04</t>
         </is>
       </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6353,6 +7038,11 @@
           <t>2026-07-29 11:06:05</t>
         </is>
       </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6396,6 +7086,11 @@
           <t>2026-07-29 11:06:08</t>
         </is>
       </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6439,6 +7134,11 @@
           <t>2026-07-29 11:06:09</t>
         </is>
       </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6482,6 +7182,11 @@
           <t>2026-07-29 11:06:10</t>
         </is>
       </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6525,6 +7230,11 @@
           <t>2026-07-29 11:06:22</t>
         </is>
       </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6568,6 +7278,11 @@
           <t>2026-07-29 11:06:22</t>
         </is>
       </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6611,6 +7326,11 @@
           <t>2026-07-29 11:06:22</t>
         </is>
       </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6654,6 +7374,11 @@
           <t>2026-07-29 11:06:23</t>
         </is>
       </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6697,6 +7422,11 @@
           <t>2026-07-29 11:06:23</t>
         </is>
       </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6740,6 +7470,11 @@
           <t>2026-07-29 11:06:24</t>
         </is>
       </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6783,6 +7518,11 @@
           <t>2026-07-29 11:06:25</t>
         </is>
       </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6826,6 +7566,11 @@
           <t>2026-07-29 11:06:28</t>
         </is>
       </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6869,6 +7614,11 @@
           <t>2026-07-29 11:06:29</t>
         </is>
       </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6912,6 +7662,11 @@
           <t>2026-07-29 11:06:30</t>
         </is>
       </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6955,6 +7710,11 @@
           <t>2026-07-29 11:07:44</t>
         </is>
       </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6998,6 +7758,11 @@
           <t>2026-07-29 11:12:58</t>
         </is>
       </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7039,6 +7804,6695 @@
       <c r="I154" t="inlineStr">
         <is>
           <t>2026-07-29 11:14:29</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/uploads/legislacao/LEI-1031.2021.pdf</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/legislacaoView/?id=2198</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>4</v>
+      </c>
+      <c r="H155" t="n">
+        <v>200</v>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:19:16</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/uploads/legislacao/legis193.pdf</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>legis193.pdf</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/legislacaoView/?id=193</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>4</v>
+      </c>
+      <c r="H156" t="n">
+        <v>200</v>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:33:03</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/uploads//cronograma-implantao-proc-contbeis-2013.pdf</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>cronograma-implantao-proc-contbeis-2013.pdf</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/pagina/105_Cronograma-de-implementacao-dos-procedimentos-contabeis.html</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>4</v>
+      </c>
+      <c r="H157" t="n">
+        <v>404</v>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:35:18</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/concursosView/{{concurso.link}}</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Edital e demais informações</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/concursosView/?id={{concurso.id}}</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>.link}}</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>4</v>
+      </c>
+      <c r="H158" t="n">
+        <v>404</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:36:31</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/2o-QUADRIMESTRE-DE-2017.pdf</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=872</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>4</v>
+      </c>
+      <c r="H159" t="n">
+        <v>200</v>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:37:33</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/3o-QUADRIMESTRE-DE-2016.pdf</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=870</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>4</v>
+      </c>
+      <c r="H160" t="n">
+        <v>403</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:37:42</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/2o-QUADRIMESTRE-DE-2016.pdf</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=869</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>4</v>
+      </c>
+      <c r="H161" t="n">
+        <v>200</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:37:49</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/concursosView/{{concurso.link}}</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Edital e demais informações</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/concursosView/?id=32</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>.link}}</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>4</v>
+      </c>
+      <c r="H162" t="n">
+        <v>404</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:41:19</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/uploads//EDITAL-DE-CONVOCACAO-PARA-ELEICAO-CAE.pdf</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Edital de Convocação para Eleição do Conselho de Alimentação Escolar</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/pagina/149_Secretaria-Municipal-de-Educacao.html</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>4</v>
+      </c>
+      <c r="H163" t="n">
+        <v>404</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:41:22</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-052.2020.pdf</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/legislacaoView/?id=1594</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>5</v>
+      </c>
+      <c r="H164" t="n">
+        <v>200</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:46:56</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-051.2020.pdf</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/legislacaoView/?id=1593</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>5</v>
+      </c>
+      <c r="H165" t="n">
+        <v>200</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:47:04</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-047.2020.pdf</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/legislacaoView/?id=1580</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>5</v>
+      </c>
+      <c r="H166" t="n">
+        <v>200</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>2026-07-29 11:47:20</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/uploads//Anexo-Anual-12-2010.pdf</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Anexo-Anual-12-2010.pdf</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/pagina/106_Anexo-Anual-2010.html</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>5</v>
+      </c>
+      <c r="H167" t="n">
+        <v>404</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:01:58</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/uploads//Anexo-Anual-13-2010.pdf</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Anexo-Anual-13-2010.pdf</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/pagina/106_Anexo-Anual-2010.html</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>5</v>
+      </c>
+      <c r="H168" t="n">
+        <v>404</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:01:59</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/uploads//Anexo-Anual-14-2010.pdf</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Anexo-Anual-14-2010.pdf</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/pagina/106_Anexo-Anual-2010.html</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>5</v>
+      </c>
+      <c r="H169" t="n">
+        <v>404</v>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:02:00</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/uploads//Anexo-Anual-15-2010.pdf</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Anexo-Anual-15-2010.pdf</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/pagina/106_Anexo-Anual-2010.html</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>5</v>
+      </c>
+      <c r="H170" t="n">
+        <v>404</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:02:01</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/uploads//Anexo-Anual-12-2011-.pdf</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Anexo-Anual-12-2011-.pdf</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/pagina/107_Anexo-Anual-2011.html</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>5</v>
+      </c>
+      <c r="H171" t="n">
+        <v>404</v>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:02:02</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/uploads//Anexo-Anual-13-2011.pdf</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Anexo-Anual-13-2011.pdf</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/pagina/107_Anexo-Anual-2011.html</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>5</v>
+      </c>
+      <c r="H172" t="n">
+        <v>404</v>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:02:03</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/uploads//Anexo-Anual-14-2011.pdf</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Anexo-Anual-14-2011.pdf</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/pagina/107_Anexo-Anual-2011.html</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>5</v>
+      </c>
+      <c r="H173" t="n">
+        <v>404</v>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:02:04</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/uploads//Anexo-Anual-15-2011.pdf</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Anexo-Anual-15-2011.pdf</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/pagina/107_Anexo-Anual-2011.html</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>5</v>
+      </c>
+      <c r="H174" t="n">
+        <v>404</v>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:02:05</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/uploads//Anexo-14---Balano.pdf</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Anexo-14---Balano.pdf</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/pagina/108_Anexo-Anual-2013.html</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>5</v>
+      </c>
+      <c r="H175" t="n">
+        <v>404</v>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:02:07</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads//Vaga-de-Creche.doc</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Informativo sobre o Ensino de Educação Infantil</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/pagina/121_Escala-Pessoal-Unidade-Basica-de-Saude.html</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>.doc</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>5</v>
+      </c>
+      <c r="H176" t="n">
+        <v>200</v>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:02:32</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads//Vaga-de-Creche_(188).doc</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Informativo sobre Vagas da Creche na Educação Infantil</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/pagina/208_Informativo-sobre-Vagas-de-Creche-na-Educacao-Infantil.html</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>.doc</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>5</v>
+      </c>
+      <c r="H177" t="n">
+        <v>200</v>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:02:39</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads//Vaga-de-Creche.pdf</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Vaga-de-Creche.pdf</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/pagina/208_Informativo-sobre-Vagas-de-Creche-na-Educacao-Infantil.html</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>5</v>
+      </c>
+      <c r="H178" t="n">
+        <v>200</v>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:02:39</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads//Plano-Municipal-de-Educacao-2015-2025.pdf</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Plano Municipal de Educação</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/pagina/209_Plano-Municipal-de-Educacao-2015-2025.html</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>5</v>
+      </c>
+      <c r="H179" t="n">
+        <v>200</v>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:02:40</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/PORTARIA-183.2026.GESTOR-DE-CONVENIO.pdf</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=5500</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>5</v>
+      </c>
+      <c r="H180" t="n">
+        <v>200</v>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:03:20</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/PORTARIA-182.2026.pdf</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=5499</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>5</v>
+      </c>
+      <c r="H181" t="n">
+        <v>200</v>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:03:28</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/legis131.pdf</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>legis131.pdf</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=131</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>5</v>
+      </c>
+      <c r="H182" t="n">
+        <v>200</v>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:06:07</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/legis129.pdf</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>legis129.pdf</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=129</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>5</v>
+      </c>
+      <c r="H183" t="n">
+        <v>200</v>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:06:14</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/LEI-705.2010.pdf</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=127</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>5</v>
+      </c>
+      <c r="H184" t="n">
+        <v>200</v>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:06:22</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/legis112.pdf</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>legis112.pdf</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=112</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>5</v>
+      </c>
+      <c r="H185" t="n">
+        <v>200</v>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:06:39</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-041.2023</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=3666</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>.2023</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>5</v>
+      </c>
+      <c r="H186" t="n">
+        <v>200</v>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:10:46</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/LEI-999.2020.-DESMEMBRA-SECRETARIAS.pdf</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=1587</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>5</v>
+      </c>
+      <c r="H187" t="n">
+        <v>200</v>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:13:18</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/LEI-997.2020-.pdf</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=1585</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>5</v>
+      </c>
+      <c r="H188" t="n">
+        <v>403</v>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:13:26</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/LEI-996.2020.L.O.A.pdf</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=1584</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>5</v>
+      </c>
+      <c r="H189" t="n">
+        <v>200</v>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:13:34</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/LEI-995.2020.L.D.O.pdf</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=1583</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>5</v>
+      </c>
+      <c r="H190" t="n">
+        <v>200</v>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:13:42</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/legis320.pdf</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>legis320.pdf</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=320</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>5</v>
+      </c>
+      <c r="H191" t="n">
+        <v>200</v>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:15:49</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/legis322.pdf</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>legis322.pdf</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=322</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>5</v>
+      </c>
+      <c r="H192" t="n">
+        <v>200</v>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:15:57</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/legis317.pdf</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>legis317.pdf</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=317</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>5</v>
+      </c>
+      <c r="H193" t="n">
+        <v>200</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:16:05</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/legis314.pdf</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>legis314.pdf</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=314</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>5</v>
+      </c>
+      <c r="H194" t="n">
+        <v>200</v>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:16:13</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/legis235.pdf</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>legis235.pdf</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=235</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>5</v>
+      </c>
+      <c r="H195" t="n">
+        <v>200</v>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:16:38</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/PORTARIA-171.2025.pdf</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=4936</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>5</v>
+      </c>
+      <c r="H196" t="n">
+        <v>200</v>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:19:36</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/PORTARIA-169.2025.aline.pdf</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=4934</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>5</v>
+      </c>
+      <c r="H197" t="n">
+        <v>403</v>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:19:44</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/PORTARIA-101.2025.pdf</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=4927</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>5</v>
+      </c>
+      <c r="H198" t="n">
+        <v>403</v>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:19:55</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/009.2017.pdf</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=423</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>5</v>
+      </c>
+      <c r="H199" t="n">
+        <v>200</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:20:24</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/008.2017.pdf</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=422</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>5</v>
+      </c>
+      <c r="H200" t="n">
+        <v>200</v>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:20:32</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/licitacao/PREGAO-ELETRONICO-002-2026---LOCACAO-DE-CACAMBAS,-COLETA-E-TRANSPORTE-DE-RESIDUOS-URBANOS-PARA-O-ATERRO-SANITARIO-DO-MUNICIPIO-DA-FAZENDA-RIO-GRANDE--PR.pdf</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/licitacaoView/?id=820</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>5</v>
+      </c>
+      <c r="H201" t="n">
+        <v>403</v>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:23:08</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/licitacao/RECURSOS-PREGAO-002-CACAMBAS.pdf</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/licitacaoView/?id=820</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G202" t="n">
+        <v>5</v>
+      </c>
+      <c r="H202" t="n">
+        <v>200</v>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:23:09</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/licitacao/PARECER-JURIDICO-RECURSO-EMPRESA-PURUNA---PREGAO-ELETRONICO-002-2026.pdf</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/licitacaoView/?id=820</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>5</v>
+      </c>
+      <c r="H203" t="n">
+        <v>200</v>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:23:09</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/licitacao/Edital-Pregao-Eletronico-005-2025--Aquisicao--Complementar-de-Medicamentos-e-Material-de-Enfermagem.pdf</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/licitacaoView/?id=776</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G204" t="n">
+        <v>5</v>
+      </c>
+      <c r="H204" t="n">
+        <v>200</v>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:23:33</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/licitacao/EDITAL-DO-PREGAO-PRESENCIAL-No011-2018--SOFTWARE-PREVIDENCIA.pdf</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/licitacaoView/?id=257</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>5</v>
+      </c>
+      <c r="H205" t="n">
+        <v>200</v>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:25:29</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/licitacao/EDITAL-DO-PREGAO-PRESENCIAL-No004-2018-VEICULO-VAN-SECRETARIA-DE-SAUDE.pdf</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/licitacaoView/?id=246</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>5</v>
+      </c>
+      <c r="H206" t="n">
+        <v>200</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:25:42</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/licitacao/EDITAL-DO-PREGAO-PRESENCIAL-No003-2018-CONTRATACAO-OFICINEIRO--e-INSTRUTOR-DE-ATIVIDADE-S-FISICAS-CRAS.pdf</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/licitacaoView/?id=244</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G207" t="n">
+        <v>5</v>
+      </c>
+      <c r="H207" t="n">
+        <v>403</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:25:50</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/licitacao/EDITAL-PREGAO-021-2017---ASSESSORIA-TRIBUTARIA.pdf</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/licitacaoView/?id=233</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G208" t="n">
+        <v>5</v>
+      </c>
+      <c r="H208" t="n">
+        <v>403</v>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:25:59</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/licitacao/EDITAL-DO-PREGAO-PRESENCIAL-No017-2017-CONTRATACAO-OFICINEIRO-CRAS.pdf</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/licitacaoView/?id=228</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>5</v>
+      </c>
+      <c r="H209" t="n">
+        <v>200</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:26:08</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//POSICAO-DE-ESTOQUE-FARMACIA-EM-03-06-25_(147).pdf</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>ESTOQUE</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/212_Estoque-de-Medicamebnto.html</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>5</v>
+      </c>
+      <c r="H210" t="n">
+        <v>200</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:29:00</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//CENTRO-DE-SAUDE-OLIMPIO-GONCALVES-DOS-SANTOS_(863).pdf</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>CENTRO DE SAÚDE</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/212_Estoque-de-Medicamebnto.html</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>5</v>
+      </c>
+      <c r="H211" t="n">
+        <v>200</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:29:00</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//CENTRO-DE-SAUDE-PEDRO-RODRIGUES---VILA-MOTA_(108).pdf</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>CENTRO DE SAÚDE</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/212_Estoque-de-Medicamebnto.html</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>5</v>
+      </c>
+      <c r="H212" t="n">
+        <v>200</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:29:01</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//CENTRO-DE-SAUDE-ANTONIO-NEVES-DA-SILVA---PORTO-NOVO_(132).pdf</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>CENTRO DE SAÚDE</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/212_Estoque-de-Medicamebnto.html</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>5</v>
+      </c>
+      <c r="H213" t="n">
+        <v>200</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:29:01</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//DECLARACAO-004-2020.pdf</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>R.H -Declaração- Admissão de Pessoal relacionada ao enfrentamento do Coronavírus- Covid-19.</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/136_Informacoes-COVID-19.html</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>5</v>
+      </c>
+      <c r="H214" t="n">
+        <v>404</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:29:02</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//Relatorio-Secretaria-M.-de-Educacao.pdf</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Secretaria M.de Educação- Relatório de enfrentamento ao COVID-19</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/136_Informacoes-COVID-19.html</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>5</v>
+      </c>
+      <c r="H215" t="n">
+        <v>404</v>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:29:03</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//Relatorio-Secretaria-M.-de-Assistencia-Social.pdf</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Sec. M. de Ass. Social- Relatório de enfrentamento ao COVID-19</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/136_Informacoes-COVID-19.html</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>5</v>
+      </c>
+      <c r="H216" t="n">
+        <v>404</v>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:29:03</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//Plano-Mun.-de-Vacinacao-Covid-19-Adrianopolis.pdf</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Plano Municipal de Vacinação</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/158_1---Plano-de-Acao-Municipal-/Estadual-de-Vacinacao---Plano.html</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>5</v>
+      </c>
+      <c r="H217" t="n">
+        <v>404</v>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:29:04</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//LEI-1003.2021---VACINAS.pdf</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Lei 1003/2021- Ratifica o protocolo de Intenções Formando entre os Municípios Brasileiros, com a Finalidade de adquirir Vacinas para o Combate a Pandemia do Coronavírus, Medicamentos, Insumos e Equipa</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/165_4--Plano-de-Acao-Municipal-/Estadual-de-Vacinacao---Lei-sobre-a-Vacina.html</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>5</v>
+      </c>
+      <c r="H218" t="n">
+        <v>404</v>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:29:07</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//ENDERECOS-DAS-UBS_(797).pdf</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Endereço das Unidades Básicas de Saúde- UBS</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/181_5---Plano-de-Acao-Mun./Est.-de-Vacinacao--Endereco-das-UBS.html</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>5</v>
+      </c>
+      <c r="H219" t="n">
+        <v>404</v>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:29:08</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//FURA-FILA.pdf</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Denúncia sobre o Fura Fila das Vacinas -COVID-19</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/155_6---Plano-de-Acao-Mun./Est.-de-Vacinacao--Denuncia-de-Fura-Fila.html</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>5</v>
+      </c>
+      <c r="H220" t="n">
+        <v>404</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:29:09</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//VTN--ITR-2020.pdf</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>VTN - ITR 2020</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/125_VTN---VALOR-TERRA-NUA---ITR.html</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>5</v>
+      </c>
+      <c r="H221" t="n">
+        <v>404</v>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:29:20</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//INFORMATIVO----VTN--ITR-2021_(387).pdf</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>VTN - ITR 2021</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/125_VTN---VALOR-TERRA-NUA---ITR.html</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>5</v>
+      </c>
+      <c r="H222" t="n">
+        <v>404</v>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:29:21</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//INFORMATIVO----VTN--ITR-2022_(502).pdf</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>VTN -ITR 2022</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/125_VTN---VALOR-TERRA-NUA---ITR.html</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>5</v>
+      </c>
+      <c r="H223" t="n">
+        <v>404</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:29:21</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//INFORMATIVO-VTN---ITR-2023.pdf</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>VTN - ITR 2023</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/125_VTN---VALOR-TERRA-NUA---ITR.html</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>5</v>
+      </c>
+      <c r="H224" t="n">
+        <v>404</v>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:29:22</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//INFORMATIVO----VTN--ITR-2024_(463).pdf</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>VTN - ITR 2024</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/125_VTN---VALOR-TERRA-NUA---ITR.html</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>5</v>
+      </c>
+      <c r="H225" t="n">
+        <v>404</v>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:29:22</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//INFORMATIVO---VTN---ITR-2025.pdf</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>VTN - ITR 2025</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/125_VTN---VALOR-TERRA-NUA---ITR.html</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>5</v>
+      </c>
+      <c r="H226" t="n">
+        <v>200</v>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:29:22</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//Carta-de-Serviço-Adrianopolis.pdf</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Carta de Serviço</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/211_Carta-de-Servico.html</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>5</v>
+      </c>
+      <c r="H227" t="n">
+        <v>200</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:29:23</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//Portaria-370.2026_(721).pdf</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Portaria</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/218_Portaria.html</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>5</v>
+      </c>
+      <c r="H228" t="n">
+        <v>200</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:29:26</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//SIM---Lei-1.126.pdf</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Lei nº 1.126/2023</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/216_Lei.html</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>5</v>
+      </c>
+      <c r="H229" t="n">
+        <v>200</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:29:27</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//DECRETO-052.2026-COMESP.doc</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Decreto 052/2026</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/217_Decreto-052/2026.html</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>.doc</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>5</v>
+      </c>
+      <c r="H230" t="n">
+        <v>200</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:29:28</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/uploads/legislacao/PESSOAL-EM-FERIAS-(3).pdf</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/legislacaoView/?id=4464</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G231" t="n">
+        <v>6</v>
+      </c>
+      <c r="H231" t="n">
+        <v>200</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:30:52</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/legis356.pdf</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>legis356.pdf</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=356</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>6</v>
+      </c>
+      <c r="H232" t="n">
+        <v>200</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:38:47</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-004.2023.pdf</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=3153</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G233" t="n">
+        <v>6</v>
+      </c>
+      <c r="H233" t="n">
+        <v>200</v>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:41:05</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-136.2022.pdf</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=3068</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G234" t="n">
+        <v>6</v>
+      </c>
+      <c r="H234" t="n">
+        <v>403</v>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:41:26</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-131.2022.pdf</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=3010</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G235" t="n">
+        <v>6</v>
+      </c>
+      <c r="H235" t="n">
+        <v>200</v>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:41:36</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-130.2022.pdf</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=3009</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G236" t="n">
+        <v>6</v>
+      </c>
+      <c r="H236" t="n">
+        <v>200</v>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:41:43</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-128.2022.pdf</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=3005</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G237" t="n">
+        <v>6</v>
+      </c>
+      <c r="H237" t="n">
+        <v>200</v>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:41:51</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-123.2022.pdf</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=2967</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G238" t="n">
+        <v>6</v>
+      </c>
+      <c r="H238" t="n">
+        <v>200</v>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:42:08</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-102.2022.pdf</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=2730</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>6</v>
+      </c>
+      <c r="H239" t="n">
+        <v>403</v>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:42:27</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-101.2022.pdf</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=2727</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G240" t="n">
+        <v>6</v>
+      </c>
+      <c r="H240" t="n">
+        <v>200</v>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:42:35</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-077.2022.pdf</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=2623</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G241" t="n">
+        <v>6</v>
+      </c>
+      <c r="H241" t="n">
+        <v>403</v>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:42:57</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-076.2022.pdf</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=2620</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G242" t="n">
+        <v>6</v>
+      </c>
+      <c r="H242" t="n">
+        <v>403</v>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:43:05</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-067.2022.pdf</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=2582</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G243" t="n">
+        <v>6</v>
+      </c>
+      <c r="H243" t="n">
+        <v>200</v>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:43:28</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-062.2022.pdf</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=2577</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G244" t="n">
+        <v>6</v>
+      </c>
+      <c r="H244" t="n">
+        <v>200</v>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:43:43</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-061.2022.pdf</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=2576</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G245" t="n">
+        <v>6</v>
+      </c>
+      <c r="H245" t="n">
+        <v>200</v>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:43:50</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-059.2022.pdf</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=2574</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G246" t="n">
+        <v>6</v>
+      </c>
+      <c r="H246" t="n">
+        <v>200</v>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:43:58</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-056.2022.pdf</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=2571</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G247" t="n">
+        <v>6</v>
+      </c>
+      <c r="H247" t="n">
+        <v>200</v>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:44:07</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-055.2022.pdf</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=2570</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G248" t="n">
+        <v>6</v>
+      </c>
+      <c r="H248" t="n">
+        <v>200</v>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:44:14</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-013.2022.pdf</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=2467</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G249" t="n">
+        <v>6</v>
+      </c>
+      <c r="H249" t="n">
+        <v>200</v>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:44:51</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-012.2022.pdf</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=2442</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G250" t="n">
+        <v>6</v>
+      </c>
+      <c r="H250" t="n">
+        <v>403</v>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:44:58</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-011.2022.pdf</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=2438</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G251" t="n">
+        <v>6</v>
+      </c>
+      <c r="H251" t="n">
+        <v>200</v>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:45:06</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-097.2021.pdf</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=2196</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G252" t="n">
+        <v>6</v>
+      </c>
+      <c r="H252" t="n">
+        <v>403</v>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:45:42</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-086.2021.pdf</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=2168</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G253" t="n">
+        <v>6</v>
+      </c>
+      <c r="H253" t="n">
+        <v>200</v>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:46:13</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-085.2021.pdf</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=2163</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G254" t="n">
+        <v>6</v>
+      </c>
+      <c r="H254" t="n">
+        <v>200</v>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:46:21</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-084.2021.pdf</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=2162</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G255" t="n">
+        <v>6</v>
+      </c>
+      <c r="H255" t="n">
+        <v>200</v>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:46:28</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-078.2021.pdf</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=2129</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G256" t="n">
+        <v>6</v>
+      </c>
+      <c r="H256" t="n">
+        <v>200</v>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:46:38</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/DECRETO-039.2021.pdf</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=1997</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G257" t="n">
+        <v>6</v>
+      </c>
+      <c r="H257" t="n">
+        <v>200</v>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:47:07</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/PORTARIA-60.2025.JULIA.pdf</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=4876</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G258" t="n">
+        <v>6</v>
+      </c>
+      <c r="H258" t="n">
+        <v>403</v>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:50:02</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/PORTARIA-51.2025.ALDINEI.pdf</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=4867</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G259" t="n">
+        <v>6</v>
+      </c>
+      <c r="H259" t="n">
+        <v>200</v>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:50:15</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/PORTARIA-50.2025.JULIA.pdf</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=4866</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G260" t="n">
+        <v>6</v>
+      </c>
+      <c r="H260" t="n">
+        <v>200</v>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:50:22</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/PORTARIA-012.2018.pdf</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=726</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G261" t="n">
+        <v>6</v>
+      </c>
+      <c r="H261" t="n">
+        <v>200</v>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:54:05</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/383.2017.pdf</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=632</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>6</v>
+      </c>
+      <c r="H262" t="n">
+        <v>200</v>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:54:32</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/194.2017.pdf</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=565</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>6</v>
+      </c>
+      <c r="H263" t="n">
+        <v>403</v>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:55:21</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/179.2017-A-191.2017.pdf</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=562</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>6</v>
+      </c>
+      <c r="H264" t="n">
+        <v>403</v>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:55:30</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/169.2017.pdf</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=552</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>6</v>
+      </c>
+      <c r="H265" t="n">
+        <v>403</v>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:55:43</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/163.2017.pdf</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=546</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>6</v>
+      </c>
+      <c r="H266" t="n">
+        <v>200</v>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:55:54</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/162.2017.pdf</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=545</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>6</v>
+      </c>
+      <c r="H267" t="n">
+        <v>200</v>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:56:01</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/161.2017.pdf</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=544</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>6</v>
+      </c>
+      <c r="H268" t="n">
+        <v>200</v>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:56:09</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/044.2017.pdf</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=458</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>6</v>
+      </c>
+      <c r="H269" t="n">
+        <v>403</v>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:57:19</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/041.2017.pdf</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=455</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>6</v>
+      </c>
+      <c r="H270" t="n">
+        <v>403</v>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:57:28</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads/legislacao/LEI-1.298.2026.PSS-Quilombolas.pdf</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/legislacaoView/?id=5569</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>6</v>
+      </c>
+      <c r="H271" t="n">
+        <v>200</v>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:59:12</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/PORTARIA-196.2024.pdf</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=4224</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>7</v>
+      </c>
+      <c r="H272" t="n">
+        <v>200</v>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:12:49</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/PORTARIA-101.2019.pdf</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=1080</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>7</v>
+      </c>
+      <c r="H273" t="n">
+        <v>200</v>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:16:08</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//Vaga-de-Creche.doc</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Informativo sobre o Ensino de Educação Infantil</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/121_Escala-Pessoal-Unidade-Basica-de-Saude.html</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>.doc</t>
+        </is>
+      </c>
+      <c r="G274" t="n">
+        <v>7</v>
+      </c>
+      <c r="H274" t="n">
+        <v>200</v>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:17:03</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//Vaga-de-Creche_(188).doc</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Informativo sobre Vagas da Creche na Educação Infantil</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/208_Informativo-sobre-Vagas-de-Creche-na-Educacao-Infantil.html</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>.doc</t>
+        </is>
+      </c>
+      <c r="G275" t="n">
+        <v>7</v>
+      </c>
+      <c r="H275" t="n">
+        <v>200</v>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:17:13</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//Vaga-de-Creche.pdf</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Vaga-de-Creche.pdf</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/208_Informativo-sobre-Vagas-de-Creche-na-Educacao-Infantil.html</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G276" t="n">
+        <v>7</v>
+      </c>
+      <c r="H276" t="n">
+        <v>200</v>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:17:13</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads//Plano-Municipal-de-Educacao-2015-2025.pdf</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Plano Municipal de Educação</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/209_Plano-Municipal-de-Educacao-2015-2025.html</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G277" t="n">
+        <v>7</v>
+      </c>
+      <c r="H277" t="n">
+        <v>200</v>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:17:15</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads/legislacao/LEI-1.246.2025.pdf</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/legislacaoView/?id=5216</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G278" t="n">
+        <v>7</v>
+      </c>
+      <c r="H278" t="n">
+        <v>200</v>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:24:47</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads/legislacao/PORTARIA-495.2025.pdf</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/legislacaoView/?id=5240</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G279" t="n">
+        <v>7</v>
+      </c>
+      <c r="H279" t="n">
+        <v>200</v>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:26:29</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads/legislacao/LEI-1052.2022.ADRIPREV.pdf</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/legislacaoView/?id=2481</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G280" t="n">
+        <v>8</v>
+      </c>
+      <c r="H280" t="n">
+        <v>200</v>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:00:52</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads/legislacao/legis391.pdf</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>legis391.pdf</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/legislacaoView/?id=391</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G281" t="n">
+        <v>8</v>
+      </c>
+      <c r="H281" t="n">
+        <v>200</v>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:04:09</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads/legislacao/legis78.pdf</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>legis78.pdf</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/legislacaoView/?id=78</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G282" t="n">
+        <v>8</v>
+      </c>
+      <c r="H282" t="n">
+        <v>200</v>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:05:20</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads/legislacao/legis19.pdf</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>legis19.pdf</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/legislacaoView/?id=19</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G283" t="n">
+        <v>8</v>
+      </c>
+      <c r="H283" t="n">
+        <v>200</v>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:06:00</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads/legislacao/PORTARIA-331.2025.pdf</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/legislacaoView/?id=5101</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G284" t="n">
+        <v>8</v>
+      </c>
+      <c r="H284" t="n">
+        <v>200</v>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:07:11</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads/legislacao/004.2017.pdf</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/legislacaoView/?id=418</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G285" t="n">
+        <v>8</v>
+      </c>
+      <c r="H285" t="n">
+        <v>200</v>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:08:42</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads/legislacao/016.2017_(161).pdf</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/legislacaoView/?id=651</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G286" t="n">
+        <v>8</v>
+      </c>
+      <c r="H286" t="n">
+        <v>200</v>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:09:56</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads/legislacao/legis167.pdf</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>legis167.pdf</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/legislacaoView/?id=167</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G287" t="n">
+        <v>8</v>
+      </c>
+      <c r="H287" t="n">
+        <v>200</v>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:11:53</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/PORTARIA-031.2021.pdf</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=1740</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G288" t="n">
+        <v>9</v>
+      </c>
+      <c r="H288" t="n">
+        <v>200</v>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:26:07</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads/legislacao/164.2017.pdf</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/legislacaoView/?id=547</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G289" t="n">
+        <v>9</v>
+      </c>
+      <c r="H289" t="n">
+        <v>200</v>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:43:06</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/legislacao/PORTARIA-228.2022.pdf</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/legislacaoView/?id=2590</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G290" t="n">
+        <v>10</v>
+      </c>
+      <c r="H290" t="n">
+        <v>200</v>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:47:49</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads/legislacao/PORTARIA-N-210.2024.pdf</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/legislacaoView/?id=4280</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G291" t="n">
+        <v>10</v>
+      </c>
+      <c r="H291" t="n">
+        <v>200</v>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:52:12</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads/legislacao/PORTARIA-209.2024.pdf</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/legislacaoView/?id=4257</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G292" t="n">
+        <v>10</v>
+      </c>
+      <c r="H292" t="n">
+        <v>403</v>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:52:20</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads/legislacao/PORTARIA-201.2024.pdf</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/legislacaoView/?id=4233</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G293" t="n">
+        <v>10</v>
+      </c>
+      <c r="H293" t="n">
+        <v>200</v>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>2026-07-29 14:52:32</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads/legislacao/PORTARIA-042.2020.pdf</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>www.adrianopolis.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Arquivo</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/legislacaoView/?id=1320</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G294" t="n">
+        <v>10</v>
+      </c>
+      <c r="H294" t="n">
+        <v>200</v>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>2026-07-30 00:05:08</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>TIPO_IGNORADO</t>
         </is>
       </c>
     </row>
